--- a/site/HR-ITSM-Manage-Engine-Service-Desk-Plus-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Manage-Engine-Service-Desk-Plus-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,50 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01M5Y9E2ZA082S5JZ91GDMCRTE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M5Y9E2ZA082S5JZ91GDMCRTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Supported Attributes for Change event</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01M5Y9EFYCF88SXBMGEBZ7XW93</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M5Y9EFYCF88SXBMGEBZ7XW93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
